--- a/artfynd/A 2592-2024 artfynd.xlsx
+++ b/artfynd/A 2592-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,12 +678,7 @@
         <v>115021695</v>
       </c>
       <c r="B2" t="n">
-        <v>90897</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92509</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -777,32 +772,27 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>115021692</v>
+        <v>38732</v>
       </c>
       <c r="B3" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>56766</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>100109</v>
+        <v>100077</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Utter</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lutra lutra</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -811,16 +801,21 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>färsk spillning</t>
+        </is>
+      </c>
       <c r="P3" t="inlineStr">
         <is>
-          <t>Norra Skärvången, Jmt</t>
+          <t>Skärvångsån, Jmt</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>469617</v>
+        <v>469869</v>
       </c>
       <c r="R3" t="n">
-        <v>7076982</v>
+        <v>7076385</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -847,17 +842,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2024-03-05</t>
+          <t>2007-10-03</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Inv faunapassager</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -872,27 +867,22 @@
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Tomas Bergström</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Benny Öwre</t>
+          <t>Via Tomas Bergström</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>115021691</v>
+        <v>115021690</v>
       </c>
       <c r="B4" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -924,10 +914,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>469794</v>
+        <v>469807</v>
       </c>
       <c r="R4" t="n">
-        <v>7076729</v>
+        <v>7076714</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -964,7 +954,7 @@
       </c>
       <c r="AC4" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Ringhack äldre</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -991,15 +981,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>115021693</v>
+        <v>115021691</v>
       </c>
       <c r="B5" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1007,21 +992,21 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>5432</v>
+        <v>100109</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Granticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Porodaedalea chrysoloma</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1031,10 +1016,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>469757</v>
+        <v>469794</v>
       </c>
       <c r="R5" t="n">
-        <v>7076761</v>
+        <v>7076729</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1067,6 +1052,11 @@
       <c r="AA5" t="inlineStr">
         <is>
           <t>2024-03-05</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1093,15 +1083,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>115021690</v>
+        <v>115021692</v>
       </c>
       <c r="B6" t="n">
-        <v>57265</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>57953</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1133,10 +1118,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>469807</v>
+        <v>469617</v>
       </c>
       <c r="R6" t="n">
-        <v>7076714</v>
+        <v>7076982</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1173,7 +1158,7 @@
       </c>
       <c r="AC6" t="inlineStr">
         <is>
-          <t>Ringhack äldre</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1197,108 +1182,6 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
-    </row>
-    <row r="7">
-      <c r="A7" t="n">
-        <v>115021694</v>
-      </c>
-      <c r="B7" t="n">
-        <v>90350</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E7" t="n">
-        <v>5432</v>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>Granticka</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>Porodaedalea chrysoloma</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>(Fr.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr"/>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>Norra Skärvången, Jmt</t>
-        </is>
-      </c>
-      <c r="Q7" t="n">
-        <v>469717</v>
-      </c>
-      <c r="R7" t="n">
-        <v>7076662</v>
-      </c>
-      <c r="S7" t="n">
-        <v>10</v>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>Krokom</t>
-        </is>
-      </c>
-      <c r="V7" t="inlineStr">
-        <is>
-          <t>Jämtland</t>
-        </is>
-      </c>
-      <c r="W7" t="inlineStr">
-        <is>
-          <t>Föllinge</t>
-        </is>
-      </c>
-      <c r="Y7" t="inlineStr">
-        <is>
-          <t>2024-03-05</t>
-        </is>
-      </c>
-      <c r="AA7" t="inlineStr">
-        <is>
-          <t>2024-03-05</t>
-        </is>
-      </c>
-      <c r="AD7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG7" t="b">
-        <v>0</v>
-      </c>
-      <c r="AT7" t="inlineStr"/>
-      <c r="AW7" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>Benny Öwre</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 2592-2024 artfynd.xlsx
+++ b/artfynd/A 2592-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115021695</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -876,6 +886,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/38732</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -978,6 +993,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115021690</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1080,6 +1100,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115021691</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1182,8 +1207,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/115021692</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>